--- a/pregenerated_results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/pregenerated_results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -474,19 +474,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3799150250048412</v>
+        <v>0.3814097435289842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04038171163066601</v>
+        <v>0.2161633346665067</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3007668702087358</v>
+        <v>-0.04227039241736896</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4590631798009466</v>
+        <v>0.8050898794753372</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.1201745152354571</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
